--- a/data/APAC/TestData.xlsx
+++ b/data/APAC/TestData.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\judip\PycharmProjects\Ecomm_POM_Project\data\APAC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3CC75B-FC98-4D68-B783-23DBC98DEC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4F1D73C-C64D-4D0A-9CD3-68A5B821B8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HomePage" sheetId="1" r:id="rId1"/>
+    <sheet name="CheckoutPage" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
   <si>
     <t>Test_ID</t>
   </si>
@@ -52,6 +53,72 @@
   </si>
   <si>
     <t>Headphones</t>
+  </si>
+  <si>
+    <t>CheckOutPage_Test_001</t>
+  </si>
+  <si>
+    <t>CheckOutPage_Test_002</t>
+  </si>
+  <si>
+    <t>FULL_NAME</t>
+  </si>
+  <si>
+    <t>ADDRESS</t>
+  </si>
+  <si>
+    <t>CITY</t>
+  </si>
+  <si>
+    <t>ZIP_CODE</t>
+  </si>
+  <si>
+    <t>DELIVERY_OPTION</t>
+  </si>
+  <si>
+    <t>FAST_SHIPPING</t>
+  </si>
+  <si>
+    <t>PAYMENT_METHOD</t>
+  </si>
+  <si>
+    <t>J UKP</t>
+  </si>
+  <si>
+    <t>Santhapet</t>
+  </si>
+  <si>
+    <t>Chittoor</t>
+  </si>
+  <si>
+    <t>Deliver to Home</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Credit/Debit Card</t>
+  </si>
+  <si>
+    <t>Collect from Store</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>PayPal</t>
+  </si>
+  <si>
+    <t>Totapalyam</t>
+  </si>
+  <si>
+    <t>J Prasad</t>
+  </si>
+  <si>
+    <t>Smart Watch Pro</t>
+  </si>
+  <si>
+    <t>CHECKOUT_PRODUCT_NAME</t>
   </si>
 </sst>
 </file>
@@ -440,4 +507,140 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8350414F-72F6-4453-960A-FE93664C452C}">
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2">
+        <v>517004</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3">
+        <v>517004</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>